--- a/crates/reg-build/fixture/inputs/lisa/variabellista.xlsx
+++ b/crates/reg-build/fixture/inputs/lisa/variabellista.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RTB</t>
+          <t>Hushållsregistret, RTB</t>
         </is>
       </c>
     </row>
